--- a/booking_forms/032_taxi_online_booking--booking_forms.xlsx
+++ b/booking_forms/032_taxi_online_booking--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,8 +750,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'one_way',_'label':_'one_way'}</t>
+          <t>one_way</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'One way', 'label': 'One way'}</t>
+          <t>One way</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'return',_'label':_'return'}</t>
+          <t>return</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Return', 'label': 'Return'}</t>
+          <t>Return</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'one_day',_'label':_'one_day'}</t>
+          <t>one_day</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'One day', 'label': 'One day'}</t>
+          <t>One day</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'multiple',_'label':_'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Multiple', 'label': 'Multiple'}</t>
+          <t>Multiple</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sedan',_'label':_'sedan'}</t>
+          <t>sedan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sedan', 'label': 'Sedan'}</t>
+          <t>Sedan</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'minivan',_'label':_'minivan'}</t>
+          <t>minivan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Minivan', 'label': 'Minivan'}</t>
+          <t>Minivan</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'luxury',_'label':_'luxury'}</t>
+          <t>luxury</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Luxury', 'label': 'Luxury'}</t>
+          <t>Luxury</t>
         </is>
       </c>
     </row>
